--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文件\战舰少女\WSGR_simulation\depend\environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C5DED4-2199-4CE5-8E12-38ADB8D071E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5E1E50-012F-4724-8E4A-2B8AE9853D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="121">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -482,6 +482,10 @@
   </si>
   <si>
     <t>U国无视战损</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>航速</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -531,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -543,7 +547,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="fill" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -827,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -835,11 +838,10 @@
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="10.25" customWidth="1"/>
     <col min="5" max="5" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="5" customWidth="1"/>
-    <col min="17" max="21" width="9" style="5"/>
+    <col min="17" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -880,31 +882,34 @@
         <v>9</v>
       </c>
       <c r="N1" t="s">
+        <v>120</v>
+      </c>
+      <c r="O1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -929,14 +934,14 @@
       <c r="L2">
         <v>5</v>
       </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="P2" s="3" t="s">
+      <c r="O2">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -958,17 +963,17 @@
       <c r="L3">
         <v>5</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.03</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -990,14 +995,14 @@
       <c r="L4">
         <v>5</v>
       </c>
-      <c r="N4">
-        <v>5</v>
-      </c>
-      <c r="P4" s="3" t="s">
+      <c r="O4">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -1022,17 +1027,17 @@
       <c r="M5">
         <v>3</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.03</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="R5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1057,14 +1062,14 @@
       <c r="L6">
         <v>5</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.03</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1083,12 +1088,12 @@
       <c r="L7">
         <v>5</v>
       </c>
-      <c r="N7">
-        <v>5</v>
-      </c>
-      <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="O7">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1110,17 +1115,17 @@
       <c r="L8">
         <v>5</v>
       </c>
-      <c r="N8">
-        <v>5</v>
-      </c>
       <c r="O8">
+        <v>5</v>
+      </c>
+      <c r="P8">
         <v>0.03</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -1148,20 +1153,20 @@
       <c r="M9">
         <v>10</v>
       </c>
-      <c r="N9">
-        <v>5</v>
-      </c>
       <c r="O9">
+        <v>5</v>
+      </c>
+      <c r="P9">
         <v>0.05</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="Q9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q9" s="5" t="s">
+      <c r="R9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -1186,14 +1191,14 @@
       <c r="M10">
         <v>3</v>
       </c>
-      <c r="N10">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3" t="s">
+      <c r="O10">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -1227,14 +1232,14 @@
       <c r="M11">
         <v>3</v>
       </c>
-      <c r="N11">
-        <v>5</v>
-      </c>
-      <c r="P11" s="3" t="s">
+      <c r="O11">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -1262,21 +1267,21 @@
       <c r="M12" s="2">
         <v>3</v>
       </c>
-      <c r="O12" s="2">
+      <c r="P12" s="2">
         <v>0.03</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="Q12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-    </row>
-    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+    </row>
+    <row r="13" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -1298,21 +1303,21 @@
       <c r="L13" s="2">
         <v>5</v>
       </c>
-      <c r="N13" s="2">
-        <v>5</v>
-      </c>
       <c r="O13" s="2">
+        <v>5</v>
+      </c>
+      <c r="P13" s="2">
         <v>0.03</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="Q13" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-    </row>
-    <row r="14" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+    </row>
+    <row r="14" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>95</v>
       </c>
@@ -1340,13 +1345,13 @@
       <c r="M14" s="2">
         <v>3</v>
       </c>
-      <c r="P14" s="4"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-    </row>
-    <row r="15" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Q14" s="4"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+    </row>
+    <row r="15" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -1374,21 +1379,21 @@
       <c r="M15" s="2">
         <v>3</v>
       </c>
-      <c r="N15" s="2">
-        <v>5</v>
-      </c>
       <c r="O15" s="2">
+        <v>5</v>
+      </c>
+      <c r="P15" s="2">
         <v>0.05</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="Q15" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-    </row>
-    <row r="16" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+    </row>
+    <row r="16" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -1416,18 +1421,18 @@
       <c r="M16" s="2">
         <v>5</v>
       </c>
-      <c r="O16" s="2">
+      <c r="P16" s="2">
         <v>0.05</v>
       </c>
-      <c r="P16" s="4" t="s">
+      <c r="Q16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-    </row>
-    <row r="17" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+    </row>
+    <row r="17" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1452,19 +1457,19 @@
       <c r="L17" s="2">
         <v>5</v>
       </c>
-      <c r="O17" s="2">
+      <c r="P17" s="2">
         <v>0.03</v>
       </c>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="2" t="s">
+      <c r="Q17" s="4"/>
+      <c r="R17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-    </row>
-    <row r="18" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+    </row>
+    <row r="18" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>99</v>
       </c>
@@ -1486,21 +1491,21 @@
       <c r="L18" s="2">
         <v>5</v>
       </c>
-      <c r="O18" s="2">
+      <c r="P18" s="2">
         <v>0.03</v>
       </c>
-      <c r="P18" s="4" t="s">
+      <c r="Q18" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-    </row>
-    <row r="19" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+    </row>
+    <row r="19" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -1525,18 +1530,18 @@
       <c r="L19" s="2">
         <v>5</v>
       </c>
-      <c r="O19" s="2">
+      <c r="P19" s="2">
         <v>0.03</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="Q19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-    </row>
-    <row r="20" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+    </row>
+    <row r="20" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>101</v>
       </c>
@@ -1567,18 +1572,18 @@
       <c r="M20" s="2">
         <v>3</v>
       </c>
-      <c r="O20" s="2">
+      <c r="P20" s="2">
         <v>0.03</v>
       </c>
-      <c r="P20" s="4" t="s">
+      <c r="Q20" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-    </row>
-    <row r="21" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+    </row>
+    <row r="21" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -1606,18 +1611,18 @@
       <c r="L21" s="2">
         <v>5</v>
       </c>
-      <c r="O21" s="2">
+      <c r="P21" s="2">
         <v>0.03</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="Q21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-    </row>
-    <row r="22" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+    </row>
+    <row r="22" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -1645,21 +1650,21 @@
       <c r="M22" s="2">
         <v>3</v>
       </c>
-      <c r="O22" s="2">
+      <c r="P22" s="2">
         <v>0.03</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="Q22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-    </row>
-    <row r="23" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+    </row>
+    <row r="23" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -1687,21 +1692,21 @@
       <c r="M23" s="2">
         <v>3</v>
       </c>
-      <c r="O23" s="2">
+      <c r="P23" s="2">
         <v>0.03</v>
       </c>
-      <c r="P23" s="4" t="s">
+      <c r="Q23" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -1717,14 +1722,14 @@
       <c r="F24">
         <v>15</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>0.3</v>
       </c>
-      <c r="P24" s="5" t="s">
+      <c r="Q24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1740,14 +1745,14 @@
       <c r="F25">
         <v>20</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>0.3</v>
       </c>
-      <c r="P25" s="5" t="s">
+      <c r="Q25" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -1763,14 +1768,14 @@
       <c r="F26">
         <v>25</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>0.3</v>
       </c>
-      <c r="P26" s="5" t="s">
+      <c r="Q26" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1783,11 +1788,11 @@
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="U27" s="5" t="s">
+      <c r="V27" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1800,7 +1805,7 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="R28" s="6" t="b">
+      <c r="S28" s="5" t="b">
         <v>1</v>
       </c>
     </row>

--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文件\战舰少女\WSGR_simulation\depend\environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5E1E50-012F-4724-8E4A-2B8AE9853D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AF8D56-DC6C-4155-B634-8C0607CBA5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1716,9 +1716,6 @@
       <c r="D24" t="s">
         <v>50</v>
       </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
       <c r="F24">
         <v>15</v>
       </c>
@@ -1739,9 +1736,6 @@
       <c r="D25" t="s">
         <v>56</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
       <c r="F25">
         <v>20</v>
       </c>
@@ -1762,9 +1756,6 @@
       <c r="D26" t="s">
         <v>57</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
       <c r="F26">
         <v>25</v>
       </c>
@@ -1785,9 +1776,6 @@
       <c r="D27" t="s">
         <v>59</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
       <c r="V27" t="s">
         <v>60</v>
       </c>
@@ -1801,9 +1789,6 @@
       </c>
       <c r="D28" t="s">
         <v>119</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
       </c>
       <c r="S28" s="5" t="b">
         <v>1</v>

--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -1,518 +1,1195 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文件\战舰少女\WSGR_simulation\depend\environment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/LING-hard/Codes/WSGR/depend/environment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AF8D56-DC6C-4155-B634-8C0607CBA5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FFE773-1FE1-BF45-8F95-300B0527516B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="工程局" sheetId="1" r:id="rId1"/>
+    <sheet name="额外加成" sheetId="2" r:id="rId2"/>
+    <sheet name="菜谱" sheetId="4" r:id="rId3"/>
+    <sheet name="摆件" sheetId="6" r:id="rId4"/>
+    <sheet name="赛车" sheetId="7" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="377">
   <si>
     <t>名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>国籍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>舰种</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>生效</t>
   </si>
   <si>
     <t>火力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼雷</t>
   </si>
   <si>
     <t>装甲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鱼雷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对空</t>
+  </si>
+  <si>
+    <t>对潜</t>
+  </si>
+  <si>
+    <t>命中</t>
   </si>
   <si>
     <t>回避</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对潜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>索敌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>航速</t>
   </si>
   <si>
     <t>幸运</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>暴击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>伤害提升</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>受伤降低</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>无视战损</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>无视补给</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必中</t>
+  </si>
+  <si>
+    <t>参与阶段</t>
   </si>
   <si>
     <t>Engineering_DD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>DD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱逐</t>
+  </si>
+  <si>
+    <t>SecondTorpedoPhase:0.05</t>
   </si>
   <si>
     <t>Engineering_ASDG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ASDG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参与阶段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>必中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SecondTorpedoPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导驱</t>
   </si>
   <si>
     <t>FirstMissilePhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AirPhase:-0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Engineering_AADG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AADG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防驱</t>
   </si>
   <si>
     <t>SecondMissilePhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Engineering_SS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜艇</t>
   </si>
   <si>
     <t>TorpedoPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AntiSubPhase:-0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Engineering_SC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炮潜</t>
+  </si>
+  <si>
+    <t>TorpedoPhase:0.05;ShellingPhase:0.05</t>
   </si>
   <si>
     <t>Engineering_AP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补给</t>
   </si>
   <si>
     <t>Engineering_BM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>BM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重炮</t>
   </si>
   <si>
     <t>ShellingPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Engineering_SSG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SSG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导潜</t>
+  </si>
+  <si>
+    <t>TorpedoPhase:0.1;NightPhase:0.1</t>
   </si>
   <si>
     <t>ShellingPhase:-0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Engineering_CVL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CVL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻母</t>
   </si>
   <si>
     <t>AntiSubPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineering_CL</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>轻巡</t>
+  </si>
+  <si>
+    <t>Engineering_CA</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>重巡</t>
+  </si>
+  <si>
+    <t>SecondTorpedoPhase:0.05;ShellingPhase:0.05</t>
+  </si>
+  <si>
+    <t>Engineering_CLT</t>
+  </si>
+  <si>
+    <t>CLT</t>
+  </si>
+  <si>
+    <t>雷巡</t>
+  </si>
+  <si>
+    <t>FirstTorpedoPhase:0.05</t>
+  </si>
+  <si>
+    <t>Engineering_CAV</t>
+  </si>
+  <si>
+    <t>CAV</t>
+  </si>
+  <si>
+    <t>航巡</t>
+  </si>
+  <si>
+    <t>Engineering_KP</t>
+  </si>
+  <si>
+    <t>KP</t>
+  </si>
+  <si>
+    <t>导巡</t>
+  </si>
+  <si>
+    <t>FirstMissilePhase:0.05;ShellingPhase:0.05;NightPhase:0.05</t>
+  </si>
+  <si>
+    <t>Engineering_CG</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>防巡</t>
+  </si>
+  <si>
+    <t>SecondMissilePhase:0.05;ShellingPhase:0.05;NightPhase:0.05</t>
+  </si>
+  <si>
+    <t>Engineering_BB</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>战列</t>
+  </si>
+  <si>
+    <t>Engineering_CV</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>航母</t>
+  </si>
+  <si>
+    <t>AirPhase:0.05</t>
+  </si>
+  <si>
+    <t>ShellingPhase:-0.1</t>
+  </si>
+  <si>
+    <t>Engineering_BC</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>战巡</t>
+  </si>
+  <si>
+    <t>Engineering_AV</t>
+  </si>
+  <si>
+    <t>AV</t>
+  </si>
+  <si>
+    <t>装母</t>
+  </si>
+  <si>
+    <t>Engineering_BBV</t>
+  </si>
+  <si>
+    <t>BBV</t>
+  </si>
+  <si>
+    <t>航战</t>
+  </si>
+  <si>
+    <t>Engineering_BBG</t>
+  </si>
+  <si>
+    <t>BBG</t>
+  </si>
+  <si>
+    <t>导战</t>
+  </si>
+  <si>
+    <t>Engineering_BG</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>大巡</t>
   </si>
   <si>
     <t>Event_Large</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>LargeShip</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>大型船猪飞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AllPhase:0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Event_Mid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MidShip</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中型船猪飞</t>
+  </si>
+  <si>
+    <t>Event_Small</t>
   </si>
   <si>
     <t>SmallShip</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Event_Small</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中型船猪飞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>小型船猪飞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Event_DD_torpedo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开幕雷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>FirstTorpedoPhase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_CL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重巡</t>
-  </si>
-  <si>
-    <t>雷巡</t>
-  </si>
-  <si>
-    <t>航巡</t>
-  </si>
-  <si>
-    <t>导巡</t>
-  </si>
-  <si>
-    <t>防巡</t>
-  </si>
-  <si>
-    <t>战列</t>
-  </si>
-  <si>
-    <t>航母</t>
-  </si>
-  <si>
-    <t>战巡</t>
-  </si>
-  <si>
-    <t>装母</t>
-  </si>
-  <si>
-    <t>航战</t>
-  </si>
-  <si>
-    <t>导战</t>
-  </si>
-  <si>
-    <t>大巡</t>
-  </si>
-  <si>
-    <t>轻巡</t>
-  </si>
-  <si>
-    <t>驱逐</t>
-  </si>
-  <si>
-    <t>导驱</t>
-  </si>
-  <si>
-    <t>防驱</t>
-  </si>
-  <si>
-    <t>潜艇</t>
-  </si>
-  <si>
-    <t>炮潜</t>
-  </si>
-  <si>
-    <t>补给</t>
-  </si>
-  <si>
-    <t>重炮</t>
-  </si>
-  <si>
-    <t>导潜</t>
-  </si>
-  <si>
-    <t>轻母</t>
-  </si>
-  <si>
-    <t>TorpedoPhase:0.05;ShellingPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TorpedoPhase:0.1;NightPhase:0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SecondTorpedoPhase:0.05;ShellingPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FirstTorpedoPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FirstMissilePhase:0.05;ShellingPhase:0.05;NightPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SecondMissilePhase:0.05;ShellingPhase:0.05;NightPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShellingPhase:-0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AirPhase:0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_CA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_CLT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_CAV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_KP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_CG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_BB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_CV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_BC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_AV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_BBV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_BBG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Engineering_BG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CLT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BBV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BBG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Event_U_undamage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>U</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>U国无视战损</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>航速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dish_I_Fire</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>萨拉米披萨(I国火力+10)</t>
+  </si>
+  <si>
+    <t>Dish_S_Fire</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>红菜汤(S国火力+7)</t>
+  </si>
+  <si>
+    <t>Dish_Mid_Accuracy</t>
+  </si>
+  <si>
+    <t>海军烘豆子(中型船命中+5)</t>
+  </si>
+  <si>
+    <t>Dish_U_ShellingDamage</t>
+  </si>
+  <si>
+    <t>苹果派(U国炮击战伤害+5%)</t>
+  </si>
+  <si>
+    <t>Dish_E_Large_Antiair</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>炸鱼薯条(E国大型船对空+5)</t>
+  </si>
+  <si>
+    <t>Dish_G_BB_Armor</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>图林根肠啤酒(G国BB装甲+7)</t>
+  </si>
+  <si>
+    <t>Dish_G_TorpedoDamage</t>
+  </si>
+  <si>
+    <t>白香肠面包圈(G国鱼雷战伤害+5%)</t>
+  </si>
+  <si>
+    <t>Dish_J_DD_NightDamage</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>海军咖喱(J国DD夜战伤害+5%)</t>
+  </si>
+  <si>
+    <t>NightPhase:0.05</t>
+  </si>
+  <si>
+    <t>Dish_F_Evasion</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>马赛鱼汤(F国闪避+7)</t>
+  </si>
+  <si>
+    <t>Dish_CL_Fire</t>
+  </si>
+  <si>
+    <t>麻婆豆腐(CL火力+7)</t>
+  </si>
+  <si>
+    <t>Dish_E_Small_Fire</t>
+  </si>
+  <si>
+    <t>仰望星空派(E国小型船火力+10)</t>
+  </si>
+  <si>
+    <t>Dish_E_BC_Armor</t>
+  </si>
+  <si>
+    <t>皇家海军咸牛肉(E国BC装甲+10)</t>
+  </si>
+  <si>
+    <t>Dish_U_Middle_Fire</t>
+  </si>
+  <si>
+    <t>鱼雷果汁(U国中型船火力+7)</t>
+  </si>
+  <si>
+    <t>Dish_Small_Fire</t>
+  </si>
+  <si>
+    <t>鲱鱼罐头(小型船火力+7)</t>
+  </si>
+  <si>
+    <t>Dish_G_Middle_Fire</t>
+  </si>
+  <si>
+    <t>黑森林蛋糕(G国中型船火力+7)</t>
+  </si>
+  <si>
+    <t>Dish_I_Large_Armor</t>
+  </si>
+  <si>
+    <t>墨00尼的屁股(I国大型船装甲+10)</t>
+  </si>
+  <si>
+    <t>Dish_J_Antiair</t>
+  </si>
+  <si>
+    <t>羊羹(J国舰船对空+7)</t>
+  </si>
+  <si>
+    <t>Dish_J_Mid_Fire</t>
+  </si>
+  <si>
+    <t>炸虾天妇罗(J国中型船火力+10)</t>
+  </si>
+  <si>
+    <t>Dish_F_Armor</t>
+  </si>
+  <si>
+    <t>马卡龙(F国装甲+10)</t>
+  </si>
+  <si>
+    <t>Dish_S_Accuracy</t>
+  </si>
+  <si>
+    <t>黑列巴(S国命中+7)</t>
+  </si>
+  <si>
+    <t>Dish_DD_Speed</t>
+  </si>
+  <si>
+    <t>辣条(DD航速+3)</t>
+  </si>
+  <si>
+    <t>Dish_BB_Accuracy</t>
+  </si>
+  <si>
+    <t>什锦叉烧炒饭(BB命中+5)</t>
+  </si>
+  <si>
+    <t>Dish_CV_Accuracy</t>
+  </si>
+  <si>
+    <t>金镶玉包子(CV命中+5)</t>
+  </si>
+  <si>
+    <t>Dish_C_ShellingDamage</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>甜豆花(C国炮击战伤害+10%)</t>
+  </si>
+  <si>
+    <t>ShellingPhase:0.1</t>
+  </si>
+  <si>
+    <t>Dish_C_TorpetoDamage</t>
+  </si>
+  <si>
+    <t>咸豆花(C国鱼雷战伤害+10%)</t>
+  </si>
+  <si>
+    <t>SecondTorpedoPhase:0.1</t>
+  </si>
+  <si>
+    <t>Dish_U_BB_Fire</t>
+  </si>
+  <si>
+    <t>美式汉堡(U国BB火力+5)</t>
+  </si>
+  <si>
+    <t>Dish_E_Fire</t>
+  </si>
+  <si>
+    <t>红茶三明治(E国火力+5)</t>
+  </si>
+  <si>
+    <t>Dish_G_Fire</t>
+  </si>
+  <si>
+    <t>烤猪肘(G国火力+5)</t>
+  </si>
+  <si>
+    <t>Dish_J_Small_Torpedo</t>
+  </si>
+  <si>
+    <t>龙田烧(J国小型船鱼雷+5)</t>
+  </si>
+  <si>
+    <t>Dish_C_Evasion</t>
+  </si>
+  <si>
+    <t>汤圆(C国闪避+8)</t>
+  </si>
+  <si>
+    <t>Dish_I_Large_Speed</t>
+  </si>
+  <si>
+    <t>番茄肉酱千层面(I国大型船航速+2)</t>
+  </si>
+  <si>
+    <t>Dish_U_CV_Armor</t>
+  </si>
+  <si>
+    <t>班尼迪克蛋(U国CV装甲+7)</t>
+  </si>
+  <si>
+    <t>Dish_G_Evasion</t>
+  </si>
+  <si>
+    <t>黑麦面包扁豆汤(G国回避+5)</t>
+  </si>
+  <si>
+    <t>Dish_E_Large_Armor</t>
+  </si>
+  <si>
+    <t>红茶司康饼(E国大型船装甲+7)</t>
+  </si>
+  <si>
+    <t>Dish_J_Large_Fire</t>
+  </si>
+  <si>
+    <t>烤鱼味增汤(J国大型船火力+5)</t>
+  </si>
+  <si>
+    <t>Dish_U_CL_Fire</t>
+  </si>
+  <si>
+    <t>热狗(U国CL火力+7)</t>
+  </si>
+  <si>
+    <t>Dish_F_BB_Fire</t>
+  </si>
+  <si>
+    <t>塔坦苹果挞(F国BB火力+7)</t>
+  </si>
+  <si>
+    <t>Dish_J_Mid_TorpedoDamage</t>
+  </si>
+  <si>
+    <t>天妇罗荞麦面(J国中型船鱼雷战伤害+10%)</t>
+  </si>
+  <si>
+    <t>Dish_E_Mid_Evasion</t>
+  </si>
+  <si>
+    <t>约克郡布丁(E国中型船回避+5)</t>
+  </si>
+  <si>
+    <t>Dish_U_Large_Armor</t>
+  </si>
+  <si>
+    <t>烧烤(U国大型船装甲+5)</t>
+  </si>
+  <si>
+    <t>Dish_C_Fire</t>
+  </si>
+  <si>
+    <t>东坡肉(C国火力+11)</t>
+  </si>
+  <si>
+    <t>Dish_S_ShellingDamage</t>
+  </si>
+  <si>
+    <t>俄式饺子(S国炮击战伤害+10%)</t>
+  </si>
+  <si>
+    <t>Dish_S_Armor</t>
+  </si>
+  <si>
+    <t>俄式肉冻(S国装甲+10)</t>
+  </si>
+  <si>
+    <t>Dish_I_Antiair</t>
+  </si>
+  <si>
+    <t>威尼斯墨鱼面(I国对空+7)</t>
+  </si>
+  <si>
+    <t>胡德船模(E国BB回避+3)</t>
+  </si>
+  <si>
+    <t>咸鱼(J国DD火力+3)</t>
+  </si>
+  <si>
+    <t>002(C国幸运+3)</t>
+  </si>
+  <si>
+    <t>坎贝尔敦船模(E国DD火力+3)</t>
+  </si>
+  <si>
+    <t>海军软飞艇(U国DD索敌+3)</t>
+  </si>
+  <si>
+    <t>摩托鱼雷(I国DD鱼雷+3)</t>
+  </si>
+  <si>
+    <t>千里眼(U国CL索敌+3)</t>
+  </si>
+  <si>
+    <t>捡到的皮鞋(S国火力+3)</t>
+  </si>
+  <si>
+    <t>比叡火控仪(J国命中+2)</t>
+  </si>
+  <si>
+    <t>莫尼特(BB火力+2)</t>
+  </si>
+  <si>
+    <t>阿图岛的飞机(U国CA对空+3)</t>
+  </si>
+  <si>
+    <t>大剑（杰克）(E国BC火力+2)</t>
+  </si>
+  <si>
+    <t>长矛鱼雷(J国DD鱼雷+2)</t>
+  </si>
+  <si>
+    <t>037战列艇(C国火力+3)</t>
+  </si>
+  <si>
+    <t>马基.72(I国回避+3)</t>
+  </si>
+  <si>
+    <t>桌面战记—深海篇(所有船幸运+1)</t>
+  </si>
+  <si>
+    <t>袭击舰炮塔(G国BC火力+2)</t>
+  </si>
+  <si>
+    <t>第八鱼雷机中队(U国CV命中+2)</t>
+  </si>
+  <si>
+    <t>金笔(BB对空+2)</t>
+  </si>
+  <si>
+    <t>不列颠战机(E国对空+3)</t>
+  </si>
+  <si>
+    <t>海权(BC命中+2)</t>
+  </si>
+  <si>
+    <t>瓦伦丁(BB装甲+2)</t>
+  </si>
+  <si>
+    <t>PT快艇(U国鱼雷+3)</t>
+  </si>
+  <si>
+    <t>扭曲烟突(J国BB火力+3)</t>
+  </si>
+  <si>
+    <t>拖拉机(S国命中+3)</t>
+  </si>
+  <si>
+    <t>模拟磁带(S国CL火力+3)</t>
+  </si>
+  <si>
+    <t>战列巡洋舰(G国BB回避+2)</t>
+  </si>
+  <si>
+    <t>巨型飞艇(G国BB火力+2)</t>
+  </si>
+  <si>
+    <t>八英寸连装炮(U国命中+2)</t>
+  </si>
+  <si>
+    <t>魔鬼鱼雷(SS鱼雷+2)</t>
+  </si>
+  <si>
+    <t>骑兵之剑(F国BB火力+2)</t>
+  </si>
+  <si>
+    <t>战斗雪橇(S国回避+2)</t>
+  </si>
+  <si>
+    <t>无人机(C国命中+3)</t>
+  </si>
+  <si>
+    <t>探照灯(J国DD命中+3)</t>
+  </si>
+  <si>
+    <t>神秘炮塔(J国幸运+2)</t>
+  </si>
+  <si>
+    <t>飞天胡萝卜(U国CL回避+2)</t>
+  </si>
+  <si>
+    <t>神奇的萝卜(BB火力+1)</t>
+  </si>
+  <si>
+    <t>最初的甲板(U国CVL命中+2)</t>
+  </si>
+  <si>
+    <t>防空机炮(U国BB闪避+2)</t>
+  </si>
+  <si>
+    <t>岸防炮(G国CA火力+2)</t>
+  </si>
+  <si>
+    <t>制导武器(G国命中+2)</t>
+  </si>
+  <si>
+    <t>rc虎王(BB命中+2)</t>
+  </si>
+  <si>
+    <t>战舰“虎”(BC装甲+2)</t>
+  </si>
+  <si>
+    <t>天空惊雷(G国CV火力+5)</t>
+  </si>
+  <si>
+    <t>003(C国火力+5)</t>
+  </si>
+  <si>
+    <t>飞行圆桶(I国火力+3)</t>
+  </si>
+  <si>
+    <t>桌面战记—决战无畏之海(所有船幸运+1)</t>
+  </si>
+  <si>
+    <t>霍兰潜艇(SS鱼雷+3)</t>
+  </si>
+  <si>
+    <t>炊事拖车(S国装甲+2)</t>
+  </si>
+  <si>
+    <t>智能地狱猫(CV回避+3)</t>
+  </si>
+  <si>
+    <t>水中杀手(DD鱼雷+3)</t>
+  </si>
+  <si>
+    <t>陆地巡洋舰(G国BC装甲+5)</t>
+  </si>
+  <si>
+    <t>弹道导弹(E国对空+10)</t>
+  </si>
+  <si>
+    <t>尼恩发动机(S国对空+10)</t>
+  </si>
+  <si>
+    <t>鱼雷快艇(C国鱼雷+5)</t>
+  </si>
+  <si>
+    <t>新动力(G国对空+10)</t>
+  </si>
+  <si>
+    <t>长空利剑(C国对空+10)</t>
+  </si>
+  <si>
+    <t>cbm鱼雷艇(C国鱼雷+3)</t>
+  </si>
+  <si>
+    <t>利爪(G国CV火力+5)</t>
+  </si>
+  <si>
+    <t>无畏舰主炮(BB火力+3)</t>
+  </si>
+  <si>
+    <t>北极星(U国SS索敌+2)</t>
+  </si>
+  <si>
+    <t>水柜(E国装甲+5)</t>
+  </si>
+  <si>
+    <t>滑行鱼雷艇(S国DD鱼雷+5)</t>
+  </si>
+  <si>
+    <t>T-34/85(S国装甲+5)</t>
+  </si>
+  <si>
+    <t>胜利仪式(C国幸运+9)</t>
+  </si>
+  <si>
+    <t>鹰击(C国火力+5)</t>
+  </si>
+  <si>
+    <t>雄鹰展翅(C国对空+10)</t>
+  </si>
+  <si>
+    <t>翱翔天际(C国幸运+6)</t>
+  </si>
+  <si>
+    <t>铁甲飞碟(S国装甲+5)</t>
+  </si>
+  <si>
+    <t>小型船鱼雷+5</t>
+  </si>
+  <si>
+    <t>所有船航速+1</t>
+  </si>
+  <si>
+    <t>大型船火力+5</t>
+  </si>
+  <si>
+    <t>所有船幸运+5</t>
+  </si>
+  <si>
+    <t>所有船对空+5</t>
+  </si>
+  <si>
+    <t>大型船装甲+7</t>
+  </si>
+  <si>
+    <t>所有船回避+5</t>
+  </si>
+  <si>
+    <t>所有船命中+5</t>
+  </si>
+  <si>
+    <t>Collection_E_BB_Evasion</t>
+  </si>
+  <si>
+    <t>Collection_J_DD_Fire</t>
+  </si>
+  <si>
+    <t>Collection_C_Luck</t>
+  </si>
+  <si>
+    <t>Collection_E_DD_Fire</t>
+  </si>
+  <si>
+    <t>Collection_U_DD_Recon</t>
+  </si>
+  <si>
+    <t>Collection_I_DD_Torpedo</t>
+  </si>
+  <si>
+    <t>Collection_U_CL_Recon</t>
+  </si>
+  <si>
+    <t>Collection_S_Fire</t>
+  </si>
+  <si>
+    <t>Collection_J_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_BB_Fire</t>
+  </si>
+  <si>
+    <t>Collection_U_CA_Antiair</t>
+  </si>
+  <si>
+    <t>Collection_E_BC_Fire</t>
+  </si>
+  <si>
+    <t>Collection_J_DD_Torpedo</t>
+  </si>
+  <si>
+    <t>Collection_C_Fire</t>
+  </si>
+  <si>
+    <t>Collection_I_Evasion</t>
+  </si>
+  <si>
+    <t>Collection_Luck</t>
+  </si>
+  <si>
+    <t>Collection_G_BC_Fire</t>
+  </si>
+  <si>
+    <t>Collection_U_CV_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_BB_Antiair</t>
+  </si>
+  <si>
+    <t>Collection_E_Antiair</t>
+  </si>
+  <si>
+    <t>Collection_BC_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_BB_Armor</t>
+  </si>
+  <si>
+    <t>Collection_U_Torpedo</t>
+  </si>
+  <si>
+    <t>Collection_J_BB_Fire</t>
+  </si>
+  <si>
+    <t>Collection_S_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_S_CL_Fire</t>
+  </si>
+  <si>
+    <t>Collection_G_BB_Evasion</t>
+  </si>
+  <si>
+    <t>Collection_G_BB_Fire</t>
+  </si>
+  <si>
+    <t>Collection_U_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_SS_Torpedo</t>
+  </si>
+  <si>
+    <t>Collection_F_BB_Fire</t>
+  </si>
+  <si>
+    <t>Collection_S_Evasion</t>
+  </si>
+  <si>
+    <t>Collection_C_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_J_DD_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_J_Luck</t>
+  </si>
+  <si>
+    <t>Collection_U_CL_Evasion</t>
+  </si>
+  <si>
+    <t>Collection_BB_Fire_1</t>
+  </si>
+  <si>
+    <t>Collection_U_CVL_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_U_BB_Evasion</t>
+  </si>
+  <si>
+    <t>Collection_G_CA_Fire</t>
+  </si>
+  <si>
+    <t>Collection_G_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_BB_Accuracy</t>
+  </si>
+  <si>
+    <t>Collection_BC_Armor</t>
+  </si>
+  <si>
+    <t>Collection_G_CV_Fire</t>
+  </si>
+  <si>
+    <t>Collection_C_Fire_1</t>
+  </si>
+  <si>
+    <t>Collection_I_Fire</t>
+  </si>
+  <si>
+    <t>Collection_Luck_1</t>
+  </si>
+  <si>
+    <t>Collection_SS_Torpedo_1</t>
+  </si>
+  <si>
+    <t>Collection_S_Armor</t>
+  </si>
+  <si>
+    <t>Collection_CV_Evasion</t>
+  </si>
+  <si>
+    <t>Collection_DD_Torpedo</t>
+  </si>
+  <si>
+    <t>Collection_G_BC_Armor</t>
+  </si>
+  <si>
+    <t>Collection_E_Antiair_1</t>
+  </si>
+  <si>
+    <t>Collection_S_Antiair</t>
+  </si>
+  <si>
+    <t>Collection_C_Torpedo</t>
+  </si>
+  <si>
+    <t>Collection_G_Antiair</t>
+  </si>
+  <si>
+    <t>Collection_C_Antiair</t>
+  </si>
+  <si>
+    <t>Collection_C_Torpedo_1</t>
+  </si>
+  <si>
+    <t>Collection_G_CV_Fire_1</t>
+  </si>
+  <si>
+    <t>Collection_BB_Fire_2</t>
+  </si>
+  <si>
+    <t>Collection_U_SS_Recon</t>
+  </si>
+  <si>
+    <t>Collection_E_Armor</t>
+  </si>
+  <si>
+    <t>Collection_S_DD_Torpedo</t>
+  </si>
+  <si>
+    <t>Collection_S_Armor_1</t>
+  </si>
+  <si>
+    <t>Collection_C_Luck_1</t>
+  </si>
+  <si>
+    <t>Collection_C_Fire_2</t>
+  </si>
+  <si>
+    <t>Collection_C_Antiair_1</t>
+  </si>
+  <si>
+    <t>Collection_C_Luck_2</t>
+  </si>
+  <si>
+    <t>Collection_S_Armor_2</t>
+  </si>
+  <si>
+    <t>Car_SmallShip_Torpedo</t>
+  </si>
+  <si>
+    <t>Car_Speed</t>
+  </si>
+  <si>
+    <t>Car_LargeShip_Fire</t>
+  </si>
+  <si>
+    <t>Car_Luck</t>
+  </si>
+  <si>
+    <t>Car_Antiair</t>
+  </si>
+  <si>
+    <t>Car_LargeShip_Armor</t>
+  </si>
+  <si>
+    <t>Car_Evasion</t>
+  </si>
+  <si>
+    <t>Car_Accuracy</t>
+  </si>
+  <si>
+    <t>鱼雷海</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣地亚哥专属</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cid(157)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Event_SanDiego</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllPhase:2.18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -535,9 +1212,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -550,6 +1227,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -610,74 +1288,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -689,23 +1307,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -715,23 +1333,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -739,26 +1357,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -793,17 +1408,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -820,28 +1435,23 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="5.625" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="10.25" customWidth="1"/>
-    <col min="5" max="5" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" customWidth="1"/>
     <col min="17" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -852,72 +1462,72 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
       <c r="N1" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -938,18 +1548,18 @@
         <v>5</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -967,21 +1577,21 @@
         <v>0.03</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -999,18 +1609,18 @@
         <v>5</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1031,21 +1641,21 @@
         <v>0.03</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1066,18 +1676,18 @@
         <v>0.03</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1093,15 +1703,15 @@
       </c>
       <c r="Q7" s="3"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1122,18 +1732,18 @@
         <v>0.03</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1160,21 +1770,21 @@
         <v>0.05</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="R9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1195,18 +1805,18 @@
         <v>5</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
         <v>61</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1236,18 +1846,18 @@
         <v>5</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1271,25 +1881,25 @@
         <v>0.03</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12"/>
       <c r="V12"/>
     </row>
-    <row r="13" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1310,22 +1920,22 @@
         <v>0.03</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="S13"/>
       <c r="T13"/>
       <c r="U13"/>
       <c r="V13"/>
     </row>
-    <row r="14" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1351,15 +1961,15 @@
       <c r="U14"/>
       <c r="V14"/>
     </row>
-    <row r="15" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1386,22 +1996,22 @@
         <v>0.05</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="S15"/>
       <c r="T15"/>
       <c r="U15"/>
       <c r="V15"/>
     </row>
-    <row r="16" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1425,22 +2035,22 @@
         <v>0.05</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="S16"/>
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16"/>
     </row>
-    <row r="17" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1462,22 +2072,22 @@
       </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S17"/>
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17"/>
     </row>
-    <row r="18" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1495,25 +2105,25 @@
         <v>0.03</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="S18"/>
       <c r="T18"/>
       <c r="U18"/>
       <c r="V18"/>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1534,22 +2144,22 @@
         <v>0.03</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="S19"/>
       <c r="T19"/>
       <c r="U19"/>
       <c r="V19"/>
     </row>
-    <row r="20" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1576,22 +2186,22 @@
         <v>0.03</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="S20"/>
       <c r="T20"/>
       <c r="U20"/>
       <c r="V20"/>
     </row>
-    <row r="21" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1615,22 +2225,22 @@
         <v>0.03</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="S21"/>
       <c r="T21"/>
       <c r="U21"/>
       <c r="V21"/>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1654,25 +2264,25 @@
         <v>0.03</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S22"/>
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22"/>
     </row>
-    <row r="23" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" s="2" customFormat="1">
       <c r="A23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1696,107 +2306,2655 @@
         <v>0.03</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="S23"/>
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:V7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F2">
+        <v>15</v>
+      </c>
+      <c r="P2">
+        <v>0.3</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="P3">
+        <v>0.3</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4">
+        <v>25</v>
+      </c>
+      <c r="P4">
+        <v>0.3</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="V5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" t="s">
+        <v>119</v>
+      </c>
+      <c r="S6" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="H7">
+        <v>53</v>
+      </c>
+      <c r="I7">
+        <v>106</v>
+      </c>
+      <c r="K7">
+        <v>53</v>
+      </c>
+      <c r="L7">
+        <v>106</v>
+      </c>
+      <c r="P7">
+        <v>0.53</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:V45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="30.1640625" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="17" max="17" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="3"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="3"/>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" s="2" customFormat="1">
+      <c r="A12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E12"/>
+      <c r="F12" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="3"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+    </row>
+    <row r="13" spans="1:22" s="2" customFormat="1">
+      <c r="A13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13"/>
+      <c r="H13" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="3"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+    </row>
+    <row r="14" spans="1:22" s="2" customFormat="1">
+      <c r="A14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14"/>
+      <c r="F14" s="2">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="4"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+    </row>
+    <row r="15" spans="1:22" s="2" customFormat="1">
+      <c r="A15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15"/>
+      <c r="F15" s="2">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="4"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+    </row>
+    <row r="16" spans="1:22" s="2" customFormat="1">
+      <c r="A16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16"/>
+      <c r="F16" s="2">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+    </row>
+    <row r="17" spans="1:22" s="2" customFormat="1">
+      <c r="A17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17"/>
+      <c r="H17" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="4"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+    </row>
+    <row r="18" spans="1:22" s="2" customFormat="1">
+      <c r="A18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E18"/>
+      <c r="I18" s="2">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="4"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+    </row>
+    <row r="19" spans="1:22" s="2" customFormat="1">
+      <c r="A19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19"/>
+      <c r="F19" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="4"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+    </row>
+    <row r="20" spans="1:22" s="2" customFormat="1">
+      <c r="A20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20"/>
+      <c r="H20" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="4"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+    </row>
+    <row r="21" spans="1:22" s="2" customFormat="1">
+      <c r="A21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E21"/>
+      <c r="K21" s="2">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="4"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+    </row>
+    <row r="22" spans="1:22" s="2" customFormat="1">
+      <c r="A22" t="s">
+        <v>167</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22"/>
+      <c r="N22" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="4"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+    </row>
+    <row r="23" spans="1:22" s="2" customFormat="1">
+      <c r="A23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23"/>
+      <c r="K23" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="4"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="K24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="A27" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
+      <c r="A28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
+      <c r="A29" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
+      <c r="A30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
+      <c r="A31" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" t="s">
+        <v>174</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="A32" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="L34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" t="s">
+        <v>200</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" t="s">
+        <v>206</v>
+      </c>
+      <c r="B40" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="L40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" t="s">
+        <v>210</v>
+      </c>
+      <c r="B42" t="s">
+        <v>174</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F42">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" t="s">
+        <v>212</v>
+      </c>
+      <c r="B43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+      <c r="B44" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" t="s">
+        <v>216</v>
+      </c>
+      <c r="B45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I45">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:V70"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="28.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="17" max="17" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>218</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="3"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" t="s">
+        <v>220</v>
+      </c>
+      <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="3"/>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>222</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>223</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>224</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" t="s">
+        <v>225</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" t="s">
+        <v>226</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" t="s">
+        <v>227</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" s="2" customFormat="1">
+      <c r="A12" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E12"/>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+    </row>
+    <row r="13" spans="1:22" s="2" customFormat="1">
+      <c r="A13" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>229</v>
+      </c>
+      <c r="E13"/>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="3"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+    </row>
+    <row r="14" spans="1:22" s="2" customFormat="1">
+      <c r="A14" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14"/>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="4"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+    </row>
+    <row r="15" spans="1:22" s="2" customFormat="1">
+      <c r="A15" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15"/>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="4"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+    </row>
+    <row r="16" spans="1:22" s="2" customFormat="1">
+      <c r="A16" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16"/>
+      <c r="D16" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16"/>
+      <c r="L16">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+    </row>
+    <row r="17" spans="1:22" s="2" customFormat="1">
+      <c r="A17" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C17"/>
+      <c r="D17" t="s">
+        <v>233</v>
+      </c>
+      <c r="E17"/>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="4"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+    </row>
+    <row r="18" spans="1:22" s="2" customFormat="1">
+      <c r="A18" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" t="s">
+        <v>234</v>
+      </c>
+      <c r="E18"/>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="4"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+    </row>
+    <row r="19" spans="1:22" s="2" customFormat="1">
+      <c r="A19" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>235</v>
+      </c>
+      <c r="E19"/>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="4"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+    </row>
+    <row r="20" spans="1:22" s="2" customFormat="1">
+      <c r="A20" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>236</v>
+      </c>
+      <c r="E20"/>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="4"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+    </row>
+    <row r="21" spans="1:22" s="2" customFormat="1">
+      <c r="A21" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" t="s">
+        <v>237</v>
+      </c>
+      <c r="E21"/>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="4"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+    </row>
+    <row r="22" spans="1:22" s="2" customFormat="1">
+      <c r="A22" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22"/>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="4"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+    </row>
+    <row r="23" spans="1:22" s="2" customFormat="1">
+      <c r="A23" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" t="s">
+        <v>239</v>
+      </c>
+      <c r="E23"/>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="4"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s">
-        <v>50</v>
-      </c>
-      <c r="F24">
+        <v>240</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" t="s">
+        <v>241</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
+        <v>242</v>
+      </c>
+      <c r="K26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="A27" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" t="s">
+        <v>243</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
+      <c r="A28" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" t="s">
+        <v>244</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
+      <c r="A29" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B29" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" t="s">
+        <v>245</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
+      <c r="A30" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>246</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
+      <c r="A31" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s">
+        <v>247</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="A32" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" t="s">
+        <v>248</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" t="s">
+        <v>249</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D34" t="s">
+        <v>250</v>
+      </c>
+      <c r="K34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" t="s">
+        <v>251</v>
+      </c>
+      <c r="K35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" t="s">
+        <v>252</v>
+      </c>
+      <c r="O36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" t="s">
+        <v>253</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" t="s">
+        <v>254</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" t="s">
+        <v>255</v>
+      </c>
+      <c r="K39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
+        <v>256</v>
+      </c>
+      <c r="L40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" t="s">
+        <v>134</v>
+      </c>
+      <c r="D42" t="s">
+        <v>258</v>
+      </c>
+      <c r="K42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C43" t="s">
+        <v>83</v>
+      </c>
+      <c r="D43" t="s">
+        <v>259</v>
+      </c>
+      <c r="K43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C44" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" t="s">
+        <v>260</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" t="s">
+        <v>261</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B46" t="s">
+        <v>174</v>
+      </c>
+      <c r="D46" t="s">
+        <v>262</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" t="s">
+        <v>263</v>
+      </c>
+      <c r="F47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="O48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" t="s">
+        <v>265</v>
+      </c>
+      <c r="G49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B50" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" t="s">
+        <v>266</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C51" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" t="s">
+        <v>267</v>
+      </c>
+      <c r="L51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C52" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" t="s">
+        <v>268</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" t="s">
+        <v>269</v>
+      </c>
+      <c r="H53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B54" t="s">
+        <v>131</v>
+      </c>
+      <c r="D54" t="s">
+        <v>270</v>
+      </c>
+      <c r="I54">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B55" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" t="s">
+        <v>271</v>
+      </c>
+      <c r="I55">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B56" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" t="s">
+        <v>272</v>
+      </c>
+      <c r="G56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B57" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57" t="s">
+        <v>273</v>
+      </c>
+      <c r="I57">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B58" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" t="s">
+        <v>274</v>
+      </c>
+      <c r="I58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B59" t="s">
+        <v>174</v>
+      </c>
+      <c r="D59" t="s">
+        <v>275</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B60" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" t="s">
+        <v>276</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C61" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" t="s">
+        <v>277</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
+      <c r="A62" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B62" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" t="s">
+        <v>278</v>
+      </c>
+      <c r="M62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B63" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" t="s">
+        <v>279</v>
+      </c>
+      <c r="H63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B64" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" t="s">
+        <v>280</v>
+      </c>
+      <c r="G64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B65" t="s">
+        <v>124</v>
+      </c>
+      <c r="D65" t="s">
+        <v>281</v>
+      </c>
+      <c r="H65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B66" t="s">
+        <v>174</v>
+      </c>
+      <c r="D66" t="s">
+        <v>282</v>
+      </c>
+      <c r="O66">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B67" t="s">
+        <v>174</v>
+      </c>
+      <c r="D67" t="s">
+        <v>283</v>
+      </c>
+      <c r="F67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B68" t="s">
+        <v>174</v>
+      </c>
+      <c r="D68" t="s">
+        <v>284</v>
+      </c>
+      <c r="I68">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B69" t="s">
+        <v>174</v>
+      </c>
+      <c r="D69" t="s">
+        <v>285</v>
+      </c>
+      <c r="O69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B70" t="s">
+        <v>124</v>
+      </c>
+      <c r="D70" t="s">
+        <v>286</v>
+      </c>
+      <c r="H70">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:V45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="17" max="17" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="P24">
-        <v>0.3</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25">
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="P25">
-        <v>0.3</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-      <c r="P26">
-        <v>0.3</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" t="s">
-        <v>59</v>
-      </c>
-      <c r="V27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" t="s">
-        <v>119</v>
-      </c>
-      <c r="S28" s="5" t="b">
+      <c r="V1" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="N3">
         <v>1</v>
       </c>
+      <c r="Q3" s="3"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="3"/>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="K9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="D10" s="2"/>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="D11" s="2"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" s="2" customFormat="1">
+      <c r="A12"/>
+      <c r="E12"/>
+      <c r="Q12" s="3"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+    </row>
+    <row r="13" spans="1:22" s="2" customFormat="1">
+      <c r="A13"/>
+      <c r="E13"/>
+      <c r="Q13" s="3"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+    </row>
+    <row r="14" spans="1:22" s="2" customFormat="1">
+      <c r="A14"/>
+      <c r="C14"/>
+      <c r="E14"/>
+      <c r="Q14" s="4"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+    </row>
+    <row r="15" spans="1:22" s="2" customFormat="1">
+      <c r="A15"/>
+      <c r="E15"/>
+      <c r="Q15" s="4"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+    </row>
+    <row r="16" spans="1:22" s="2" customFormat="1">
+      <c r="A16"/>
+      <c r="C16"/>
+      <c r="E16"/>
+      <c r="Q16" s="4"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+    </row>
+    <row r="17" spans="1:22" s="2" customFormat="1">
+      <c r="A17"/>
+      <c r="C17"/>
+      <c r="E17"/>
+      <c r="Q17" s="4"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+    </row>
+    <row r="18" spans="1:22" s="2" customFormat="1">
+      <c r="A18"/>
+      <c r="E18"/>
+      <c r="Q18" s="4"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+    </row>
+    <row r="19" spans="1:22" s="2" customFormat="1">
+      <c r="A19"/>
+      <c r="C19"/>
+      <c r="E19"/>
+      <c r="Q19" s="4"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+    </row>
+    <row r="20" spans="1:22" s="2" customFormat="1">
+      <c r="A20"/>
+      <c r="E20"/>
+      <c r="Q20" s="4"/>
+      <c r="S20"/>
+      <c r="T20"/>
+      <c r="U20"/>
+      <c r="V20"/>
+    </row>
+    <row r="21" spans="1:22" s="2" customFormat="1">
+      <c r="A21"/>
+      <c r="E21"/>
+      <c r="Q21" s="4"/>
+      <c r="S21"/>
+      <c r="T21"/>
+      <c r="U21"/>
+      <c r="V21"/>
+    </row>
+    <row r="22" spans="1:22" s="2" customFormat="1">
+      <c r="A22"/>
+      <c r="E22"/>
+      <c r="Q22" s="4"/>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+    </row>
+    <row r="23" spans="1:22" s="2" customFormat="1">
+      <c r="A23"/>
+      <c r="E23"/>
+      <c r="Q23" s="4"/>
+      <c r="S23"/>
+      <c r="T23"/>
+      <c r="U23"/>
+      <c r="V23"/>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:22">
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:22">
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:22">
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:22">
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="4:4">
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="4:4">
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="4:4">
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="4:4">
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="4:4">
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="4:4">
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="4:4">
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="4:4">
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="4:4">
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="4:4">
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="4:4">
+      <c r="D45" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/LING-hard/Codes/WSGR/depend/environment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FFE773-1FE1-BF45-8F95-300B0527516B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982B9338-1094-144E-8D0A-5D6FEACD8C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="380">
   <si>
     <t>名称</t>
   </si>
@@ -1159,6 +1159,18 @@
   </si>
   <si>
     <t>AllPhase:2.18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Supply_Damage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>公正的决斗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllPhase:0.3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2324,7 +2336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
@@ -2462,68 +2474,79 @@
       </c>
     </row>
     <row r="5" spans="1:22">
-      <c r="A5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
+      <c r="A5" s="6" t="s">
+        <v>377</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="V5" t="s">
-        <v>116</v>
+        <v>378</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="V6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" t="s">
         <v>117</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>118</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>119</v>
       </c>
-      <c r="S6" s="5" t="b">
+      <c r="S7" s="5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="6" t="s">
+    <row r="8" spans="1:22">
+      <c r="A8" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>53</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>53</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>106</v>
       </c>
-      <c r="K7">
+      <c r="K8">
         <v>53</v>
       </c>
-      <c r="L7">
+      <c r="L8">
         <v>106</v>
       </c>
-      <c r="P7">
+      <c r="P8">
         <v>0.53</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="Q8" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="S7" t="b">
+      <c r="S8" t="b">
         <v>1</v>
       </c>
-      <c r="T7" t="b">
+      <c r="T8" t="b">
         <v>1</v>
       </c>
     </row>

--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/LING-hard/Codes/WSGR/depend/environment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982B9338-1094-144E-8D0A-5D6FEACD8C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB69C9F5-7824-EF4C-A9A8-68A65BE12C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34980" yWindow="-500" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工程局" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="384">
   <si>
     <t>名称</t>
   </si>
@@ -1171,6 +1171,22 @@
   </si>
   <si>
     <t>AllPhase:0.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collection_C_Small_Fire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SmallShip</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>某新型主炮(C国小型船火力+8)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1224,7 +1240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1240,6 +1256,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="fill"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3400,7 +3419,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:V70"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
@@ -4597,6 +4616,23 @@
       </c>
       <c r="H70">
         <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F71">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
